--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N90_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N90_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.856839211950734</v>
+        <v>0.9517363719419943</v>
       </c>
       <c r="D2" t="n">
-        <v>5.587649738116953</v>
+        <v>0.9079930824440049</v>
       </c>
       <c r="E2" t="n">
-        <v>7.219873742524124</v>
+        <v>1.17322948316017</v>
       </c>
       <c r="F2" t="n">
-        <v>7.145608082082981</v>
+        <v>1.161161313338484</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.590818917048461</v>
+        <v>1.396008074020375</v>
       </c>
       <c r="D3" t="n">
-        <v>8.126420976465122</v>
+        <v>1.320543408675582</v>
       </c>
       <c r="E3" t="n">
-        <v>7.219873742524124</v>
+        <v>1.17322948316017</v>
       </c>
       <c r="F3" t="n">
-        <v>7.145608082082981</v>
+        <v>1.161161313338484</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.69517885402175</v>
+        <v>4.337966563778535</v>
       </c>
       <c r="D4" t="n">
-        <v>26.23456206781728</v>
+        <v>4.263116336020308</v>
       </c>
       <c r="E4" t="n">
-        <v>7.219873742524124</v>
+        <v>1.17322948316017</v>
       </c>
       <c r="F4" t="n">
-        <v>7.145608082082981</v>
+        <v>1.161161313338484</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.7541472774295</v>
+        <v>2.235048932582294</v>
       </c>
       <c r="D5" t="n">
-        <v>13.31220054873258</v>
+        <v>2.163232589169045</v>
       </c>
       <c r="E5" t="n">
-        <v>7.219873742524124</v>
+        <v>1.17322948316017</v>
       </c>
       <c r="F5" t="n">
-        <v>7.145608082082981</v>
+        <v>1.161161313338484</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.4497329536452</v>
+        <v>1.860581604967345</v>
       </c>
       <c r="D6" t="n">
-        <v>11.83610882934446</v>
+        <v>1.923367684768476</v>
       </c>
       <c r="E6" t="n">
-        <v>7.219873742524124</v>
+        <v>1.17322948316017</v>
       </c>
       <c r="F6" t="n">
-        <v>7.145608082082981</v>
+        <v>1.161161313338484</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
